--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2014/ILLINOIS_2014.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2014/ILLINOIS_2014.xlsx
@@ -2868,7 +2868,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Temosachi</t>
+          <t>Temosachic</t>
         </is>
       </c>
       <c r="C140">
@@ -6630,7 +6630,7 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C349">
@@ -6810,7 +6810,7 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C359">
@@ -15414,7 +15414,7 @@
       </c>
       <c r="B837" t="inlineStr">
         <is>
-          <t>Dr. Arroyo</t>
+          <t>Doctor Arroyo</t>
         </is>
       </c>
       <c r="C837">
@@ -18150,7 +18150,7 @@
       </c>
       <c r="B989" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C989">
@@ -19068,7 +19068,7 @@
       </c>
       <c r="B1040" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C1040">
@@ -19086,7 +19086,7 @@
       </c>
       <c r="B1041" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C1041">
@@ -20850,7 +20850,7 @@
       </c>
       <c r="B1139" t="inlineStr">
         <is>
-          <t>Santo Domingo Tonaltepec</t>
+          <t>Santo Domingo Tomaltepec</t>
         </is>
       </c>
       <c r="C1139">
@@ -27690,7 +27690,7 @@
       </c>
       <c r="B1519" t="inlineStr">
         <is>
-          <t>Altzayanca</t>
+          <t>Atltzayanca</t>
         </is>
       </c>
       <c r="C1519">
@@ -28482,7 +28482,7 @@
       </c>
       <c r="B1563" t="inlineStr">
         <is>
-          <t>Yauhquemecan</t>
+          <t>Yauhquemehcan</t>
         </is>
       </c>
       <c r="C1563">
@@ -31398,7 +31398,7 @@
       </c>
       <c r="B1725" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C1725">
